--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92571136581</v>
+        <v>46157.93107857567</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93107857567</v>
+        <v>46157.93177770176</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93177770176</v>
+        <v>46157.93402661107</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93402661107</v>
+        <v>46157.93720659761</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93720659761</v>
+        <v>46158.28218741107</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28218741107</v>
+        <v>46158.29692038749</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29692038749</v>
+        <v>46158.29817810619</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29817810619</v>
+        <v>46158.33389706831</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33389706831</v>
+        <v>46158.36859551076</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36859551076</v>
+        <v>46158.3729015713</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
